--- a/trabGramos/outputs/tables/nn_selected_analysis.xlsx
+++ b/trabGramos/outputs/tables/nn_selected_analysis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="159" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="212" uniqueCount="57">
   <si>
     <t>group_name</t>
   </si>
@@ -127,6 +127,63 @@
   </si>
   <si>
     <t>outputs\nn\selected_analysis\nn_15_5_trainbr_60_20_20_norm_test.png</t>
+  </si>
+  <si>
+    <t>nn_10_trainscg_70_15_15_raw</t>
+  </si>
+  <si>
+    <t>nn_10_trainscg_70_15_15_norm</t>
+  </si>
+  <si>
+    <t>nn_10_traingdx_70_15_15_raw</t>
+  </si>
+  <si>
+    <t>nn_8_8_4_trainscg_70_15_15_norm</t>
+  </si>
+  <si>
+    <t>nn_8_8_4_trainscg_60_20_20_norm</t>
+  </si>
+  <si>
+    <t>nn_8_8_4_trainscg_60_20_20_raw</t>
+  </si>
+  <si>
+    <t>traingdx</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_trainscg_70_15_15_raw_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_trainscg_70_15_15_norm_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_traingdx_70_15_15_raw_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_70_15_15_norm_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_60_20_20_norm_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_60_20_20_raw_global.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_trainscg_70_15_15_raw_test.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_trainscg_70_15_15_norm_test.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_10_traingdx_70_15_15_raw_test.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_70_15_15_norm_test.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_60_20_20_norm_test.png</t>
+  </si>
+  <si>
+    <t>outputs\nn\selected_analysis\nn_8_8_4_trainscg_60_20_20_raw_test.png</t>
   </si>
 </sst>
 </file>
@@ -176,7 +233,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.54296875" customWidth="true"/>
-    <col min="2" max="2" width="30.36328125" customWidth="true"/>
+    <col min="2" max="2" width="31.08984375" customWidth="true"/>
     <col min="3" max="3" width="12.6328125" customWidth="true"/>
     <col min="4" max="4" width="8.36328125" customWidth="true"/>
     <col min="5" max="5" width="12.7265625" customWidth="true"/>
@@ -184,8 +241,8 @@
     <col min="7" max="7" width="8.26953125" customWidth="true"/>
     <col min="8" max="8" width="14.08984375" customWidth="true"/>
     <col min="9" max="9" width="12.1796875" customWidth="true"/>
-    <col min="10" max="10" width="65.453125" customWidth="true"/>
-    <col min="11" max="11" width="63.54296875" customWidth="true"/>
+    <col min="10" max="10" width="66.1796875" customWidth="true"/>
+    <col min="11" max="11" width="64.26953125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -228,34 +285,34 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="0" t="b">
         <v>0</v>
       </c>
       <c r="G2" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H2" s="0">
-        <v>99.980000000000004</v>
+        <v>100</v>
       </c>
       <c r="I2" s="0">
-        <v>99.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
@@ -263,34 +320,34 @@
         <v>1</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3" s="0" t="b">
         <v>1</v>
       </c>
       <c r="G3" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="0">
-        <v>99.980000000000004</v>
+        <v>100</v>
       </c>
       <c r="I3" s="0">
-        <v>99.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="J3" s="0" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="K3" s="0" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4">
@@ -298,34 +355,34 @@
         <v>1</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="0" t="b">
         <v>0</v>
       </c>
       <c r="G4" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H4" s="0">
-        <v>99.980000000000004</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="I4" s="0">
-        <v>99.900000000000006</v>
+        <v>100</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="K4" s="0" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -333,13 +390,13 @@
         <v>2</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" s="0" t="s">
         <v>19</v>
@@ -348,19 +405,19 @@
         <v>1</v>
       </c>
       <c r="G5" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H5" s="0">
-        <v>99.960000000000008</v>
+        <v>100</v>
       </c>
       <c r="I5" s="0">
-        <v>99.733333333333334</v>
+        <v>100</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -368,34 +425,34 @@
         <v>2</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="0">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" s="0">
-        <v>99.939999999999998</v>
+        <v>100</v>
       </c>
       <c r="I6" s="0">
-        <v>99.700000000000003</v>
+        <v>100</v>
       </c>
       <c r="J6" s="0" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="K6" s="0" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -403,34 +460,34 @@
         <v>2</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" s="0" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="0" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="0">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H7" s="0">
-        <v>99.939999999999998</v>
+        <v>99.980000000000004</v>
       </c>
       <c r="I7" s="0">
-        <v>99.700000000000003</v>
+        <v>100</v>
       </c>
       <c r="J7" s="0" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K7" s="0" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
